--- a/exports/YESBANK_full_report.xlsx
+++ b/exports/YESBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44606.38541666666</v>
+        <v>44606.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>13.45</v>
+        <v>13.25</v>
       </c>
       <c r="I2" t="n">
         <v>13.38567954850989</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.93</v>
+        <v>-5.36</v>
       </c>
       <c r="L2" t="n">
         <v>6.43</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.89</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44655.38541666666</v>
+        <v>44655.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="I3" t="n">
         <v>13.02131219926905</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>48.83333333333334</v>
+        <v>49</v>
       </c>
       <c r="K3" t="n">
-        <v>2.64</v>
+        <v>1.13</v>
       </c>
       <c r="L3" t="n">
         <v>6.42</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.33</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>14.05</v>
+        <v>13.6</v>
       </c>
       <c r="I4" t="n">
         <v>13.96936656152058</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>7.25</v>
+        <v>3.82</v>
       </c>
       <c r="L4" t="n">
         <v>1.91</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.64</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44699.38541666666</v>
+        <v>44699.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>13.25</v>
+        <v>13.9</v>
       </c>
       <c r="I5" t="n">
         <v>13.46607890489399</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K5" t="n">
-        <v>2.57</v>
+        <v>-2.21</v>
       </c>
       <c r="L5" t="n">
         <v>6.25</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>10.83</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>12.75</v>
+        <v>12.55</v>
       </c>
       <c r="I6" t="n">
         <v>12.69047304040339</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.27</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>8.99</v>
+        <v>10.07</v>
       </c>
       <c r="M6" t="n">
         <v>2.88</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>6.63</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44750.55208333334</v>
+        <v>44753.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>12.75</v>
+        <v>13.2</v>
       </c>
       <c r="I7" t="n">
         <v>13.06340017485146</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.59</v>
+        <v>-5.18</v>
       </c>
       <c r="L7" t="n">
-        <v>3.98</v>
+        <v>6.37</v>
       </c>
       <c r="M7" t="n">
         <v>1.18</v>
       </c>
       <c r="N7" t="n">
-        <v>2.82</v>
+        <v>3.53</v>
       </c>
       <c r="O7" t="n">
         <v>-1.57</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.28</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44768.38541666666</v>
+        <v>44768.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>13.85</v>
+        <v>13.75</v>
       </c>
       <c r="I8" t="n">
         <v>13.79211309277249</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>4.92</v>
+        <v>4.17</v>
       </c>
       <c r="L8" t="n">
         <v>3.79</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44770.55208333334</v>
+        <v>44771.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="I9" t="n">
         <v>14.90140663984877</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.18</v>
+        <v>-9.09</v>
       </c>
       <c r="L9" t="n">
-        <v>9.09</v>
+        <v>11.27</v>
       </c>
       <c r="M9" t="n">
         <v>1.02</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.23</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44823.38541666666</v>
+        <v>44823.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="I10" t="n">
         <v>16.48814439528651</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>10.67</v>
+        <v>9.33</v>
       </c>
       <c r="L10" t="n">
         <v>2.33</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.82</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>16.25</v>
+        <v>16.55</v>
       </c>
       <c r="I11" t="n">
         <v>16.5477332826533</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>0.91</v>
+        <v>-0.91</v>
       </c>
       <c r="L11" t="n">
         <v>5.18</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.24</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44914.55208333334</v>
+        <v>44915.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>21.4</v>
+        <v>20.8</v>
       </c>
       <c r="I12" t="n">
         <v>20.96434722782395</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>74.16666666666667</v>
+        <v>75</v>
       </c>
       <c r="K12" t="n">
-        <v>29.31</v>
+        <v>25.68</v>
       </c>
       <c r="L12" t="n">
         <v>7.85</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>14.64</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44924.55208333334</v>
+        <v>44925.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>20.15</v>
+        <v>20.6</v>
       </c>
       <c r="I13" t="n">
         <v>20.48961379099238</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>3.13</v>
+        <v>0.96</v>
       </c>
       <c r="L13" t="n">
         <v>4.09</v>
       </c>
       <c r="M13" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="N13" t="n">
         <v>13.71</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>11.88</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44937.55208333334</v>
+        <v>44938.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>20.05</v>
+        <v>19.8</v>
       </c>
       <c r="I14" t="n">
         <v>19.84958056338812</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.67</v>
+        <v>-3.88</v>
       </c>
       <c r="L14" t="n">
-        <v>2.91</v>
+        <v>4.37</v>
       </c>
       <c r="M14" t="n">
         <v>0.24</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44984.55208333334</v>
+        <v>44985.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>16.35</v>
+        <v>17.35</v>
       </c>
       <c r="I15" t="n">
         <v>17.02389797860758</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K15" t="n">
-        <v>17.42</v>
+        <v>12.37</v>
       </c>
       <c r="L15" t="n">
         <v>3.79</v>
@@ -1296,7 +1475,7 @@
         <v>1.47</v>
       </c>
       <c r="N15" t="n">
-        <v>3.73</v>
+        <v>7.65</v>
       </c>
       <c r="O15" t="n">
         <v>-1.25</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.13</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44991.55208333334</v>
+        <v>44993.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>16.9</v>
+        <v>16.65</v>
       </c>
       <c r="I16" t="n">
         <v>16.87650733457183</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.59</v>
+        <v>-4.03</v>
       </c>
       <c r="L16" t="n">
         <v>6.05</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45033.55208333334</v>
+        <v>45034.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>15.35</v>
+        <v>16.25</v>
       </c>
       <c r="I17" t="n">
         <v>15.82923602735666</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K17" t="n">
-        <v>7.81</v>
+        <v>2.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.8</v>
@@ -1410,7 +1613,7 @@
         <v>0.99</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="O17" t="n">
         <v>-1.18</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45041.38541666666</v>
+        <v>45041.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="I18" t="n">
         <v>15.59325238776692</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-4</v>
+        <v>-4.62</v>
       </c>
       <c r="L18" t="n">
         <v>5.85</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>7.93</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45077.38541666666</v>
+        <v>45077.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>15.85</v>
+        <v>16.45</v>
       </c>
       <c r="I19" t="n">
         <v>16.10675648546151</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>35.83333333333334</v>
+        <v>36</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.26</v>
+        <v>-6.13</v>
       </c>
       <c r="L19" t="n">
-        <v>5.81</v>
+        <v>6.45</v>
       </c>
       <c r="M19" t="n">
         <v>0.63</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.74</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45145.38541666666</v>
+        <v>45145.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="I20" t="n">
         <v>16.89802729932565</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>67.83333333333333</v>
+        <v>68</v>
       </c>
       <c r="K20" t="n">
-        <v>3.34</v>
+        <v>2.13</v>
       </c>
       <c r="L20" t="n">
         <v>3.95</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>4.92</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45169.55208333334</v>
+        <v>45170.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>16.8</v>
+        <v>17.35</v>
       </c>
       <c r="I21" t="n">
         <v>17.33408595605423</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-3.27</v>
       </c>
       <c r="L21" t="n">
-        <v>3.87</v>
+        <v>4.76</v>
       </c>
       <c r="M21" t="n">
         <v>0.89</v>
       </c>
       <c r="N21" t="n">
-        <v>0.89</v>
+        <v>2.98</v>
       </c>
       <c r="O21" t="n">
         <v>-1.18</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.61</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45194.55208333334</v>
+        <v>45195.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>17.45</v>
+        <v>17.35</v>
       </c>
       <c r="I22" t="n">
         <v>17.38875370423282</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K22" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>3.75</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.7</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45237.38541666666</v>
+        <v>45237.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>16.75</v>
+        <v>16.85</v>
       </c>
       <c r="I23" t="n">
         <v>16.7520822623179</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K23" t="n">
-        <v>3.46</v>
+        <v>2.88</v>
       </c>
       <c r="L23" t="n">
         <v>2.88</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.2</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>21.65</v>
+        <v>20.35</v>
       </c>
       <c r="I24" t="n">
         <v>20.91799889243549</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>42.83333333333334</v>
+        <v>43</v>
       </c>
       <c r="K24" t="n">
-        <v>28.49</v>
+        <v>20.77</v>
       </c>
       <c r="L24" t="n">
         <v>0.89</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>13.51</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45289.55208333334</v>
+        <v>45292.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>21.4</v>
+        <v>22.5</v>
       </c>
       <c r="I25" t="n">
         <v>22.39232577813725</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.16</v>
+        <v>-10.57</v>
       </c>
       <c r="L25" t="n">
-        <v>7.13</v>
+        <v>13.02</v>
       </c>
       <c r="M25" t="n">
         <v>0.71</v>
       </c>
       <c r="N25" t="n">
-        <v>3.69</v>
+        <v>4.91</v>
       </c>
       <c r="O25" t="n">
         <v>-8.33</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.98</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45324.55208333334</v>
+        <v>45327.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>23.65</v>
+        <v>23.1</v>
       </c>
       <c r="I26" t="n">
         <v>23.44246022983122</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K26" t="n">
-        <v>5.11</v>
+        <v>2.67</v>
       </c>
       <c r="L26" t="n">
         <v>4.89</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>8.19</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45327.55208333334</v>
+        <v>45328.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>22.8</v>
+        <v>25.15</v>
       </c>
       <c r="I27" t="n">
         <v>24.45007421776149</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1.3</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>3.03</v>
+        <v>11.26</v>
       </c>
       <c r="M27" t="n">
-        <v>0.42</v>
+        <v>1.32</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>11.84</v>
       </c>
       <c r="O27" t="n">
         <v>-3.59</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.28</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45342.38541666666</v>
+        <v>45342.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>26.8</v>
+        <v>26.65</v>
       </c>
       <c r="I28" t="n">
         <v>26.66319242515402</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>6.56</v>
+        <v>5.96</v>
       </c>
       <c r="L28" t="n">
         <v>8.550000000000001</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>12.52</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45366.38541666666</v>
+        <v>45366.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>23.25</v>
+        <v>23.75</v>
       </c>
       <c r="I29" t="n">
         <v>23.42812293523333</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K29" t="n">
-        <v>12.76</v>
+        <v>10.88</v>
       </c>
       <c r="L29" t="n">
         <v>2.81</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>13.37</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45412.55208333334</v>
+        <v>45414.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>26.15</v>
+        <v>25.55</v>
       </c>
       <c r="I30" t="n">
         <v>25.60080729042929</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K30" t="n">
-        <v>10.11</v>
+        <v>7.58</v>
       </c>
       <c r="L30" t="n">
         <v>4</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>9.43</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>23.2</v>
+        <v>23.65</v>
       </c>
       <c r="I31" t="n">
         <v>23.61230707930327</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K31" t="n">
-        <v>9.199999999999999</v>
+        <v>7.44</v>
       </c>
       <c r="L31" t="n">
         <v>1.76</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>5.17</v>
       </c>
       <c r="N31" t="n">
         <v>2.88</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>4.7</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>23.55</v>
+        <v>22.2</v>
       </c>
       <c r="I32" t="n">
         <v>22.53882813918791</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.42</v>
+        <v>-6.13</v>
       </c>
       <c r="L32" t="n">
-        <v>1.06</v>
+        <v>11.21</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="O32" t="n">
         <v>1.51</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.52</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45455.38541666666</v>
+        <v>45455.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>24.08</v>
+        <v>24.14</v>
       </c>
       <c r="I33" t="n">
         <v>24.11696928653201</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.74</v>
       </c>
       <c r="L33" t="n">
         <v>10.36</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>7.01</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>25.52</v>
+        <v>23.6</v>
       </c>
       <c r="I34" t="n">
         <v>24.71549088339578</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>51</v>
+        <v>53.83333333333334</v>
       </c>
       <c r="K34" t="n">
-        <v>5.72</v>
+        <v>-2.24</v>
       </c>
       <c r="L34" t="n">
         <v>3.4</v>
       </c>
       <c r="M34" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>3.8</v>
+        <v>7.68</v>
       </c>
       <c r="O34" t="n">
         <v>1.94</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>11.64</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45545.55208333334</v>
+        <v>45546.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>22.97</v>
+        <v>23.92</v>
       </c>
       <c r="I35" t="n">
         <v>23.72338797626353</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K35" t="n">
-        <v>2.67</v>
+        <v>-1.36</v>
       </c>
       <c r="L35" t="n">
         <v>6.36</v>
@@ -2436,7 +2855,7 @@
         <v>2.53</v>
       </c>
       <c r="N35" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O35" t="n">
         <v>-7.68</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>6.54</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45562.55208333334</v>
+        <v>45565.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>22.77</v>
+        <v>22.51</v>
       </c>
       <c r="I36" t="n">
         <v>22.62555533389615</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.81</v>
+        <v>-5.89</v>
       </c>
       <c r="L36" t="n">
-        <v>5.31</v>
+        <v>6.06</v>
       </c>
       <c r="M36" t="n">
         <v>0.26</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>4.08</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45590.55208333334</v>
+        <v>45593.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>19.5</v>
+        <v>20.82</v>
       </c>
       <c r="I37" t="n">
         <v>20.62570616845846</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K37" t="n">
-        <v>13.37</v>
+        <v>7.51</v>
       </c>
       <c r="L37" t="n">
         <v>1.02</v>
       </c>
       <c r="M37" t="n">
-        <v>0.59</v>
+        <v>4.36</v>
       </c>
       <c r="N37" t="n">
-        <v>1.69</v>
+        <v>5.95</v>
       </c>
       <c r="O37" t="n">
         <v>-1.32</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>8.27</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45608.38541666666</v>
+        <v>45608.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>19.94</v>
+        <v>19.74</v>
       </c>
       <c r="I38" t="n">
         <v>19.75216560687221</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.23</v>
+        <v>-5.19</v>
       </c>
       <c r="L38" t="n">
-        <v>4.66</v>
+        <v>5.62</v>
       </c>
       <c r="M38" t="n">
         <v>3.37</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.97</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45622.55208333334</v>
+        <v>45623.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>20.13</v>
+        <v>20.24</v>
       </c>
       <c r="I39" t="n">
         <v>20.16456965441206</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.98</v>
+        <v>-2.53</v>
       </c>
       <c r="L39" t="n">
         <v>4.51</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.35</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>20.91</v>
+        <v>20.74</v>
       </c>
       <c r="I40" t="n">
         <v>20.76467331870727</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K40" t="n">
-        <v>3.31</v>
+        <v>2.47</v>
       </c>
       <c r="L40" t="n">
         <v>1.98</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>5.71</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>17.97</v>
+        <v>18.31</v>
       </c>
       <c r="I41" t="n">
         <v>18.30026261525021</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K41" t="n">
-        <v>13.36</v>
+        <v>11.72</v>
       </c>
       <c r="L41" t="n">
         <v>1.54</v>
       </c>
       <c r="M41" t="n">
-        <v>0.71</v>
+        <v>1.5</v>
       </c>
       <c r="N41" t="n">
         <v>5.36</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.01</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>18.63</v>
+        <v>18.04</v>
       </c>
       <c r="I42" t="n">
         <v>18.41490100401566</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K42" t="n">
-        <v>1.75</v>
+        <v>-1.47</v>
       </c>
       <c r="L42" t="n">
         <v>1.91</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.64</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>16.48</v>
+        <v>17.02</v>
       </c>
       <c r="I43" t="n">
         <v>16.94059983664983</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>8.65</v>
+        <v>5.65</v>
       </c>
       <c r="L43" t="n">
         <v>3.6</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>6.43</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>17.25</v>
+        <v>16.52</v>
       </c>
       <c r="I44" t="n">
         <v>16.67168587190512</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>1.35</v>
+        <v>-2.94</v>
       </c>
       <c r="L44" t="n">
-        <v>2.94</v>
+        <v>5.05</v>
       </c>
       <c r="M44" t="n">
-        <v>1.44</v>
+        <v>6.03</v>
       </c>
       <c r="N44" t="n">
         <v>4.11</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>7.75</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>17.56</v>
+        <v>17.97</v>
       </c>
       <c r="I45" t="n">
         <v>17.80070158519992</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.3</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>6.48</v>
+        <v>9.26</v>
       </c>
       <c r="M45" t="n">
         <v>1.98</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.98</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45772.38541666666</v>
+        <v>45772.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>17.84</v>
+        <v>17.76</v>
       </c>
       <c r="I46" t="n">
         <v>17.82459109159755</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.72</v>
+        <v>-1.17</v>
       </c>
       <c r="L46" t="n">
         <v>2.34</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.19</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45784.55208333334</v>
+        <v>45785.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>18.35</v>
+        <v>18.61</v>
       </c>
       <c r="I47" t="n">
         <v>18.56650675060954</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.32</v>
+        <v>-4.79</v>
       </c>
       <c r="L47" t="n">
         <v>9.460000000000001</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.46</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45810.55208333334</v>
+        <v>45811.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>23.23</v>
+        <v>21.02</v>
       </c>
       <c r="I48" t="n">
         <v>21.632256398805</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K48" t="n">
-        <v>24.83</v>
+        <v>12.95</v>
       </c>
       <c r="L48" t="n">
         <v>4.51</v>
@@ -3177,7 +3752,7 @@
         <v>2.14</v>
       </c>
       <c r="N48" t="n">
-        <v>1.81</v>
+        <v>9.81</v>
       </c>
       <c r="O48" t="n">
         <v>-0.87</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>13.37</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45835.55208333334</v>
+        <v>45838.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>20.22</v>
+        <v>20.42</v>
       </c>
       <c r="I49" t="n">
         <v>20.39360313938474</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K49" t="n">
-        <v>3.81</v>
+        <v>2.85</v>
       </c>
       <c r="L49" t="n">
         <v>9.09</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>4.03</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45849.38541666666</v>
+        <v>45849.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>19.74</v>
+        <v>19.65</v>
       </c>
       <c r="I50" t="n">
         <v>19.65706463347502</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.33</v>
+        <v>-3.77</v>
       </c>
       <c r="L50" t="n">
-        <v>3.67</v>
+        <v>3.97</v>
       </c>
       <c r="M50" t="n">
         <v>0.15</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>2.85</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45852.55208333334</v>
+        <v>45853.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>20.03</v>
+        <v>20.51</v>
       </c>
       <c r="I51" t="n">
         <v>20.21026824376053</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.93</v>
+        <v>-4.38</v>
       </c>
       <c r="L51" t="n">
-        <v>2.04</v>
+        <v>4.83</v>
       </c>
       <c r="M51" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="N51" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="O51" t="n">
         <v>-0.86</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>4.64</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>19.6</v>
+        <v>19.38</v>
       </c>
       <c r="I52" t="n">
         <v>19.58307800526871</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.44</v>
+        <v>-5.51</v>
       </c>
       <c r="L52" t="n">
-        <v>5.27</v>
+        <v>5.61</v>
       </c>
       <c r="M52" t="n">
         <v>0.5</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>5.42</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45888.38541666666</v>
+        <v>45888.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>19.18</v>
+        <v>19.38</v>
       </c>
       <c r="I53" t="n">
         <v>19.32642395666517</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>2.22</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>3.75</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45894.55208333334</v>
+        <v>45895.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>19.61</v>
+        <v>19.06</v>
       </c>
       <c r="I54" t="n">
         <v>19.07465300176705</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>1.19</v>
+        <v>-1.65</v>
       </c>
       <c r="L54" t="n">
-        <v>1.08</v>
+        <v>1.75</v>
       </c>
       <c r="M54" t="n">
-        <v>0.21</v>
+        <v>0.61</v>
       </c>
       <c r="N54" t="n">
-        <v>0.77</v>
+        <v>3.26</v>
       </c>
       <c r="O54" t="n">
         <v>1.36</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>5.49</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45901.38541666666</v>
+        <v>45901.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>19.35</v>
+        <v>19.56</v>
       </c>
       <c r="I55" t="n">
         <v>19.51420569898657</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.52</v>
+        <v>-2.62</v>
       </c>
       <c r="L55" t="n">
-        <v>2.57</v>
+        <v>3.04</v>
       </c>
       <c r="M55" t="n">
         <v>0.96</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.09</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45946.55208333334</v>
+        <v>45947.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>23.14</v>
+        <v>22.19</v>
       </c>
       <c r="I56" t="n">
         <v>22.7883624306521</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>45</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="K56" t="n">
-        <v>18.3</v>
+        <v>13.45</v>
       </c>
       <c r="L56" t="n">
         <v>1.18</v>
@@ -3633,7 +4304,7 @@
         <v>0.28</v>
       </c>
       <c r="N56" t="n">
-        <v>3.03</v>
+        <v>3.46</v>
       </c>
       <c r="O56" t="n">
         <v>2.09</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.1</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45964.55208333334</v>
+        <v>45965.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>22.97</v>
+        <v>23.31</v>
       </c>
       <c r="I57" t="n">
         <v>23.24687771840187</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.52</v>
+        <v>-5.05</v>
       </c>
       <c r="L57" t="n">
-        <v>4.73</v>
+        <v>5.77</v>
       </c>
       <c r="M57" t="n">
         <v>0.72</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>5.96</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45985.38541666666</v>
+        <v>45985.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>22.34</v>
+        <v>22.2</v>
       </c>
       <c r="I58" t="n">
         <v>22.24186683401392</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.16</v>
+        <v>-4.76</v>
       </c>
       <c r="L58" t="n">
-        <v>4.33</v>
+        <v>4.93</v>
       </c>
       <c r="M58" t="n">
         <v>0.53</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>3.97</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>21.48</v>
+        <v>22.15</v>
       </c>
       <c r="I59" t="n">
         <v>21.88781167710266</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>38</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K59" t="n">
-        <v>3.24</v>
+        <v>0.23</v>
       </c>
       <c r="L59" t="n">
         <v>4.46</v>
@@ -3804,7 +4511,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N59" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="O59" t="n">
         <v>-0.98</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>4.87</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46041.55208333334</v>
+        <v>46042.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>22.73</v>
+        <v>21.9</v>
       </c>
       <c r="I60" t="n">
         <v>22.3807574401681</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K60" t="n">
-        <v>2.62</v>
+        <v>-1.13</v>
       </c>
       <c r="L60" t="n">
         <v>3.02</v>
@@ -3861,7 +4580,7 @@
         <v>0.35</v>
       </c>
       <c r="N60" t="n">
-        <v>3.28</v>
+        <v>4.53</v>
       </c>
       <c r="O60" t="n">
         <v>4</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>8.4</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>18.12</v>
+        <v>18.92</v>
       </c>
       <c r="I61" t="n">
         <v>18.44818027275928</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>77.16666666666667</v>
+        <v>78</v>
       </c>
       <c r="K61" t="n">
-        <v>17.26</v>
+        <v>13.61</v>
       </c>
       <c r="L61" t="n">
         <v>3.61</v>
       </c>
       <c r="M61" t="n">
-        <v>3.48</v>
+        <v>4.19</v>
       </c>
       <c r="N61" t="n">
-        <v>3.82</v>
+        <v>5.24</v>
       </c>
       <c r="O61" t="n">
         <v>-4.53</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.14</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46162.55208333334</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>22.04</v>
+        <v>21.32</v>
       </c>
       <c r="I62" t="n">
         <v>21.34980327796319</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K62" t="n">
-        <v>16.49</v>
+        <v>12.68</v>
       </c>
       <c r="L62" t="n">
         <v>2.48</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46169.55208333334</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>22.74</v>
+        <v>23.19</v>
       </c>
       <c r="I63" t="n">
         <v>23.00508033125581</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K63" t="n">
-        <v>-6.66</v>
+        <v>-8.77</v>
       </c>
       <c r="L63" t="n">
-        <v>7.74</v>
+        <v>10.46</v>
       </c>
       <c r="M63" t="n">
         <v>1.19</v>
       </c>
       <c r="N63" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="O63" t="n">
         <v>-2</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.77</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46209.55208333334</v>
+        <v>46210.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>24.28</v>
+        <v>23.93</v>
       </c>
       <c r="I64" t="n">
         <v>23.98068014671451</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K64" t="n">
-        <v>4.7</v>
+        <v>3.19</v>
       </c>
       <c r="L64" t="n">
         <v>4.36</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.49</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46275.55208333334</v>
+        <v>46276.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>22.26</v>
+        <v>23.03</v>
       </c>
       <c r="I65" t="n">
         <v>22.59838161191113</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>65.16666666666667</v>
+        <v>66</v>
       </c>
       <c r="K65" t="n">
-        <v>6.98</v>
+        <v>3.76</v>
       </c>
       <c r="L65" t="n">
         <v>1.55</v>
@@ -4146,7 +4925,7 @@
         <v>1.49</v>
       </c>
       <c r="N65" t="n">
-        <v>1.81</v>
+        <v>6.06</v>
       </c>
       <c r="O65" t="n">
         <v>-0.95</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>5.55</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>22.48</v>
+        <v>21.5</v>
       </c>
       <c r="I66" t="n">
         <v>22.43964092791479</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.39</v>
+        <v>-6.64</v>
       </c>
       <c r="L66" t="n">
-        <v>4.17</v>
+        <v>6.9</v>
       </c>
       <c r="M66" t="n">
         <v>0.99</v>
       </c>
       <c r="N66" t="n">
-        <v>3.48</v>
+        <v>5.87</v>
       </c>
       <c r="O66" t="n">
         <v>6.06</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>7.12</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>21.14</v>
+        <v>21.29</v>
       </c>
       <c r="I67" t="n">
         <v>21.23825864909655</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K67" t="n">
-        <v>1.67</v>
+        <v>0.98</v>
       </c>
       <c r="L67" t="n">
         <v>4.09</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,25 +5111,25 @@
         <v>5.33</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46310.38541666666</v>
+        <v>46310.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>21.29</v>
+        <v>18.22</v>
       </c>
       <c r="I68" t="n">
         <v>20.15470915029498</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>-14.42</v>
       </c>
       <c r="L68" t="n">
-        <v>1.78</v>
+        <v>20.34</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N68" t="n">
         <v>13.81</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,12 @@
       <c r="Q69" t="n">
         <v>15</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7312,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7322,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7332,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77.2</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7342,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7352,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7362,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="11">
@@ -6539,7 +7372,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +7382,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6559,7 +7392,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.7</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="14">
@@ -6569,7 +7402,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.36</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7412,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.14</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7422,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.56</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7432,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.31</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7442,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>59.7</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7452,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.25</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7462,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.95</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7472,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.36</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7482,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7492,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7502,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="25">
@@ -6689,7 +7522,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.76</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="27">
@@ -6709,7 +7542,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
